--- a/ct_scoop_links_2026-04-09.xlsx
+++ b/ct_scoop_links_2026-04-09.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,17 +433,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>heading</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
@@ -443,7 +455,7 @@
           <t>STORRS SCOOP: Dog House Subs is NOW OPEN in Storrs Center</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,7 +470,7 @@
           <t>WEST HARTFORD SCOOP: Angel Land opens, bringing kid's entertainment to Corbin's Corner!</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +485,7 @@
           <t>NEWINGTON SCOOP: Ross Dress for Less eyeing new location in Newington</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -488,7 +500,7 @@
           <t>BRANFORD SCOOP: Wingstop coming soon to Branford</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -503,7 +515,7 @@
           <t>MILFORD SCOOP: Toasty Scoops coming soon to Sundae House spot</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -518,7 +530,7 @@
           <t>WALLINGFORD SCOOP: Donovan Family Confections reopening on 04/09!</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -533,7 +545,7 @@
           <t>SEEKONK SCOOP: The Ugly Dumpling coming to former TGI Fridays site</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -548,7 +560,7 @@
           <t>MANSFIELD SCOOP: Mansfield Drive-In opens for the season!</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -563,7 +575,7 @@
           <t>MANCHESTER SCOOP: Town eyeing possible round-about on Main Street, conceptual rendering shared</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -578,7 +590,7 @@
           <t>MANCHESTER SCOOP: Health Inspection Reports - January &amp; February 2026</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -593,7 +605,7 @@
           <t>STAMFORD SCOOP: PopUp Bagels coming soon to Stamford!</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -608,7 +620,7 @@
           <t>WATERFORD SCOOP: Crystal Mall update</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="C13" t="inlineStr">

--- a/ct_scoop_links_2026-04-09.xlsx
+++ b/ct_scoop_links_2026-04-09.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,17 +421,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>heading</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
@@ -455,7 +443,7 @@
           <t>STORRS SCOOP: Dog House Subs is NOW OPEN in Storrs Center</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,7 +458,7 @@
           <t>WEST HARTFORD SCOOP: Angel Land opens, bringing kid's entertainment to Corbin's Corner!</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +473,7 @@
           <t>NEWINGTON SCOOP: Ross Dress for Less eyeing new location in Newington</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +488,7 @@
           <t>BRANFORD SCOOP: Wingstop coming soon to Branford</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -515,7 +503,7 @@
           <t>MILFORD SCOOP: Toasty Scoops coming soon to Sundae House spot</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -530,7 +518,7 @@
           <t>WALLINGFORD SCOOP: Donovan Family Confections reopening on 04/09!</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -545,7 +533,7 @@
           <t>SEEKONK SCOOP: The Ugly Dumpling coming to former TGI Fridays site</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -560,7 +548,7 @@
           <t>MANSFIELD SCOOP: Mansfield Drive-In opens for the season!</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -575,7 +563,7 @@
           <t>MANCHESTER SCOOP: Town eyeing possible round-about on Main Street, conceptual rendering shared</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -590,7 +578,7 @@
           <t>MANCHESTER SCOOP: Health Inspection Reports - January &amp; February 2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -605,7 +593,7 @@
           <t>STAMFORD SCOOP: PopUp Bagels coming soon to Stamford!</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -620,7 +608,7 @@
           <t>WATERFORD SCOOP: Crystal Mall update</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C13" t="inlineStr">
